--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.30206312262661</v>
+        <v>3.461585257426824</v>
       </c>
       <c r="D2" t="n">
-        <v>21.37962458002182</v>
+        <v>3.474188994253546</v>
       </c>
       <c r="E2" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F2" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.350082459127129</v>
+        <v>0.8693883996081585</v>
       </c>
       <c r="D3" t="n">
-        <v>5.883049748933139</v>
+        <v>0.9559955842016351</v>
       </c>
       <c r="E3" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F3" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.90819983661067</v>
+        <v>5.022582473449234</v>
       </c>
       <c r="D4" t="n">
-        <v>29.5410255762143</v>
+        <v>4.800416656134824</v>
       </c>
       <c r="E4" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F4" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.49473972408297</v>
+        <v>6.092895205163483</v>
       </c>
       <c r="D5" t="n">
-        <v>35.89595908906183</v>
+        <v>5.833093351972548</v>
       </c>
       <c r="E5" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F5" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.00480724789168</v>
+        <v>4.225781177782399</v>
       </c>
       <c r="D6" t="n">
-        <v>25.02832862098647</v>
+        <v>4.067103400910303</v>
       </c>
       <c r="E6" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F6" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.55002333698326</v>
+        <v>2.52687879225978</v>
       </c>
       <c r="D7" t="n">
-        <v>14.71909402721514</v>
+        <v>2.391852779422461</v>
       </c>
       <c r="E7" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F7" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.69340638772226</v>
+        <v>10.67517853800487</v>
       </c>
       <c r="D8" t="n">
-        <v>66.32134502141388</v>
+        <v>10.77721856597976</v>
       </c>
       <c r="E8" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F8" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.17343629292557</v>
+        <v>2.953183397600404</v>
       </c>
       <c r="D9" t="n">
-        <v>18.8672047391117</v>
+        <v>3.065920770105651</v>
       </c>
       <c r="E9" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F9" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.71562991867754</v>
+        <v>6.291289861785101</v>
       </c>
       <c r="D10" t="n">
-        <v>32.76758844662984</v>
+        <v>5.32473312257735</v>
       </c>
       <c r="E10" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F10" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.9539227822762</v>
+        <v>6.167512452119883</v>
       </c>
       <c r="D11" t="n">
-        <v>38.62503767397991</v>
+        <v>6.276568622021736</v>
       </c>
       <c r="E11" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F11" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.70447731730795</v>
+        <v>7.101977564062541</v>
       </c>
       <c r="D12" t="n">
-        <v>45.30164099373014</v>
+        <v>7.361516661481148</v>
       </c>
       <c r="E12" t="n">
-        <v>15.65321616886029</v>
+        <v>2.543647627439797</v>
       </c>
       <c r="F12" t="n">
-        <v>15.6867073526902</v>
+        <v>2.549089944812157</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
